--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CUBO RODA - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CUBO RODA - 24_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,282 +493,6 @@
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7295991826644</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RAIO INOX (FREIO A DISCO) IRON TITAN CG125-150 ESD 8292</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7895099122633</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RZ IRON POP100 024513</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7895099126600</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RAIO INOX IRON BROS NXR125-150 173287</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>602883764095</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>RAIO INOX IRON BROS NXR160/ XRE190 ESD DISCO 187240</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7895099126594</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>RAIO INOX DISCO IRON NXR BROS150 173286</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7895099126587</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>RAIO INOX IRON BROS NXR125-150 173285</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>RAIO SMARTFOX BROS NXR125</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7908073702643</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>RAIO SMARTFOX CG TITAN125 2000 A 2004/ FAN150</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>7908073702322</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>RAIO SMARTFOX BROS NXR125-150</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>6941655608118</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RAIO INOX DISCO ALLEN </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7899468024511</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>RAIO TRILHA CG TITAN150 KS/ FAN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3000000018316</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>RAIO SOLIDEZ BIZ125 30000</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CUBO RODA - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CUBO RODA - 24_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -453,7 +448,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -474,7 +468,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
